--- a/examples/zips/92258/92258_sold.xlsx
+++ b/examples/zips/92258/92258_sold.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:AR2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,16 +549,116 @@
           <t>lot_sqft</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>lot_size_sqft</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>listing_description</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>hoa_fee</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>hoa_monthly_fee</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>raw_details</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>raw_tags</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>raw_photo_tags</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pool_available</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pool_type</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>is_private_pool</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>is_private_pool_known</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>private_pool_verified</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pool_conflict</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pool_community_only</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pool_confidence</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pool_signal_sources</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pool_evidence</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>has_pool_inferred</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>has_pool_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/17080-Covey-St_North-Palm-Springs_CA_92258_M20172-08695</t>
+          <t>https://www.realtor.com/realestateandhomes-detail/17364-Indian-Canyon-Dr_Palm-Springs_CA_92258_M99186-85292</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2017208695</t>
+          <t>9918685292</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -573,7 +673,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17080 Covey St</t>
+          <t>17364 Indian Canyon Dr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -596,483 +696,135 @@
           <t>Riverside</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Garnet Gardens</t>
+        </is>
+      </c>
       <c r="K2" t="n">
-        <v>33.924302</v>
+        <v>33.922302</v>
       </c>
       <c r="L2" t="n">
-        <v>-116.543857</v>
+        <v>-116.54493</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1799</v>
+        <v>1300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2007</v>
+        <v>1955</v>
       </c>
       <c r="R2" t="n">
-        <v>237</v>
+        <v>109</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2025-07-29 21:03:57</t>
+          <t>2025-11-19 20:43:40</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-24 17:40:39</t>
+          <t>2026-03-09 00:00:00</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>375000</v>
+        <v>329000</v>
       </c>
       <c r="V2" t="n">
-        <v>326000</v>
+        <v>329000</v>
       </c>
       <c r="W2" t="n">
-        <v>181</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/17364-Indian-Canyon-Dr_Palm-Springs_CA_92258_M99186-85292</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>9918685292</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SINGLE_FAMILY</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>17364 Indian Canyon Dr</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>North Palm Springs</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>92258</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>33.922302</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-116.54493</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>1300</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1955</v>
-      </c>
-      <c r="R3" t="n">
-        <v>109</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2025-11-19 20:43:40</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-03-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>329000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>329000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>253</v>
-      </c>
-      <c r="X3" t="n">
+        <v>253.0769230769231</v>
+      </c>
+      <c r="X2" t="n">
         <v>8002</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/61980-Barrel-Cactus-Rd_North-Palm-Springs_CA_92258_M29621-05194</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2962105194</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SINGLE_FAMILY</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>61980 Barrel Cactus Rd</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>North Palm Springs</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>92258</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>33.926784</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-116.580529</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="Y2" t="n">
+        <v>8002</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Come and see a new remodeld home perfect for first time buyers with big rooms and spacious floor plan.</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Come and see a new remodeld home perfect for first time buyers with big rooms and spacious floor plan.</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[{"category": "Bedrooms", "text": ["Bedrooms: 3", "Bedrooms On Main Level: 3"], "parent_category": "Interior"}, {"category": "Bathrooms", "text": ["Total Bathrooms: 2", "Full Bathrooms: 2", "Bathrooms On Main Level: 2"], "parent_category": "Interior"}, {"category": "Other Rooms", "text": ["All Bedrooms Down"], "parent_category": "Interior"}, {"category": "Appliances", "text": ["Laundry Features: Gas &amp; Electric Dryer Hookup"], "parent_category": "Interior"}, {"category": "Heating and Cooling", "text": ["Cooling Features: Central Air"], "parent_category": "Interior"}, {"category": "Land Info", "text": ["Additional Parcels: No", "Land Lease: No", "Lot Description: 0-1 Unit/Acre", "Lot Size Acres: 0.1837", "Lot Size Source: Builder", "Lot Size Square Feet: 8000"], "parent_category": "Exterior"}, {"category": "Garage and Parking", "text": ["Garage Spaces: 2", "Parking Total: 2"], "parent_category": "Exterior"}, {"category": "Home Features", "text": ["View: Mountain(s)"], "parent_category": "Exterior"}, {"category": "Homeowners Association", "text": ["Association: No", "Calculated Total Monthly Association Fees: 0"], "parent_category": "Community"}, {"category": "Multi-Unit Info", "text": ["Number of Units: 1"], "parent_category": "Community"}, {"category": "School Information", "text": ["School District: Palm Springs Unified"], "parent_category": "Community"}, {"category": "Rental Info", "text": ["Lease Considered: No"], "parent_category": "Community"}, {"category": "Amenities and Community Features", "text": ["Community Features: Valley"], "parent_category": "Community"}, {"category": "Other Property Info", "text": ["Source Listing Status: Closed", "County: Riverside", "Directions: 10frwy east get off on indian canyon dr make a left", "Source Property Type: Residential", "Area: 331 - North End Palm Springs", "Source Neighborhood: Palm Springs C.C. (33113)", "Parcel Number: 666211004", "Subdivision: Palm Springs C.C. (33113)", "Property Subtype: Single Family Residence"], "parent_category": "Listing"}, {"category": "Building and Construction", "text": ["Total Square Feet Living: 1300.00", "Year Built: 1955", "Common Walls: No Common Walls", "Entry Level: 1", "Entry Location: Side", "Levels: One", "Living Area Units: Square Feet", "Property Age: 71", "Property Attached: No", "Levels or Stories: One", "Building Total Stories: 1", "Structure Type: House", "Elevation Units: Feet", "Year Built Source: Public Records"], "parent_category": "Features"}, {"category": "Utilities", "text": ["Sewer: Public Sewer", "Water Source: Public"], "parent_category": "Features"}]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>["central_air", "hill_or_mountain_view", "laundry_room", "view", "single_story", "garage_1_or_more", "garage_2_or_more", "floor_plan"]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[{"href": "https://ap.rdcpix.com/95156bdff2ec7384f17153eddf817604l-m3627712800s.jpg", "labels": ["exterior"]}]</t>
+        </is>
+      </c>
+      <c r="AG2" t="b">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>952</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1958</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>230000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>242</v>
-      </c>
-      <c r="X4" t="n">
-        <v>21780</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/62550-16th-Ave_North-Palm-Springs_CA_92258_M24340-77939</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2434077939</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SINGLE_FAMILY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>62550 16th Ave</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>North Palm Springs</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>92258</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>33.932271</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-116.571062</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Garage Spaces: 2</t>
+        </is>
+      </c>
+      <c r="AQ2" t="b">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>480</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1959</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>175000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>365</v>
-      </c>
-      <c r="X5" t="n">
-        <v>58806</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/64665-Thumb-Dr_North-Palm-Springs_CA_92258_M29883-03152</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2988303152</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SINGLE_FAMILY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>64665 Thumb Dr</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>North Palm Springs</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>92258</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>33.922412</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-116.533448</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>2790</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1960</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>367000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>132</v>
-      </c>
-      <c r="X6" t="n">
-        <v>95832</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/17190-Covey-St_N-Palm-Spgs_CA_92258_M20172-45961</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2017245961</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SINGLE_FAMILY</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>17190 Covey St</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Palm Springs</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>92258</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>33.923464</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-116.543864</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>1123</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1960</v>
-      </c>
-      <c r="R7" t="n">
-        <v>185</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2025-01-13 21:53:50</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>380000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>332500</v>
-      </c>
-      <c r="W7" t="n">
-        <v>296</v>
-      </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
